--- a/data/data_raw/eurostat/AT_lorries_road_eqr_lormot.xlsx
+++ b/data/data_raw/eurostat/AT_lorries_road_eqr_lormot.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,11 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -571,6 +576,9 @@
       </c>
       <c r="Q2" t="n">
         <v>3772</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4447</v>
       </c>
     </row>
     <row r="3">
@@ -635,6 +643,9 @@
       <c r="Q3" t="n">
         <v>30702</v>
       </c>
+      <c r="R3" t="n">
+        <v>33088</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -698,6 +709,9 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -761,6 +775,9 @@
       <c r="Q5" t="n">
         <v>1939</v>
       </c>
+      <c r="R5" t="n">
+        <v>2169</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -824,6 +841,9 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -887,6 +907,9 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -950,6 +973,9 @@
       <c r="Q8" t="n">
         <v>3719</v>
       </c>
+      <c r="R8" t="n">
+        <v>4287</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1013,6 +1039,9 @@
       <c r="Q9" t="n">
         <v>25480</v>
       </c>
+      <c r="R9" t="n">
+        <v>27984</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1076,6 +1105,9 @@
       <c r="Q10" t="n">
         <v>10</v>
       </c>
+      <c r="R10" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1139,6 +1171,9 @@
       <c r="Q11" t="n">
         <v>2</v>
       </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1202,6 +1237,9 @@
       <c r="Q12" t="n">
         <v>43</v>
       </c>
+      <c r="R12" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1265,6 +1303,9 @@
       <c r="Q13" t="n">
         <v>3265</v>
       </c>
+      <c r="R13" t="n">
+        <v>2928</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1328,6 +1369,9 @@
       <c r="Q14" t="n">
         <v>53</v>
       </c>
+      <c r="R14" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1391,6 +1435,9 @@
       <c r="Q15" t="n">
         <v>3283</v>
       </c>
+      <c r="R15" t="n">
+        <v>2935</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1454,6 +1501,9 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1517,6 +1567,9 @@
       <c r="Q17" t="n">
         <v>1934</v>
       </c>
+      <c r="R17" t="n">
+        <v>2038</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1580,6 +1633,9 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1643,6 +1699,9 @@
       <c r="Q19" t="n">
         <v>5</v>
       </c>
+      <c r="R19" t="n">
+        <v>131</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1706,6 +1765,9 @@
       <c r="Q20" t="n">
         <v>3719</v>
       </c>
+      <c r="R20" t="n">
+        <v>4287</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1769,6 +1831,9 @@
       <c r="Q21" t="n">
         <v>25123</v>
       </c>
+      <c r="R21" t="n">
+        <v>27912</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1832,6 +1897,9 @@
       <c r="Q22" t="n">
         <v>0</v>
       </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1894,6 +1962,9 @@
       </c>
       <c r="Q23" t="n">
         <v>357</v>
+      </c>
+      <c r="R23" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -1946,6 +2017,9 @@
       <c r="Q24" t="n">
         <v>0</v>
       </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1997,6 +2071,9 @@
       <c r="Q25" t="n">
         <v>0</v>
       </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2048,6 +2125,9 @@
       <c r="Q26" t="n">
         <v>0</v>
       </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2099,6 +2179,9 @@
       <c r="Q27" t="n">
         <v>0</v>
       </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2152,6 +2235,7 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2205,6 +2289,7 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2268,6 +2353,9 @@
       <c r="Q30" t="n">
         <v>0</v>
       </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2330,6 +2418,9 @@
       </c>
       <c r="Q31" t="n">
         <v>16</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
